--- a/dgii_signature_microservice/src/utils/paso-3/datos.xlsx
+++ b/dgii_signature_microservice/src/utils/paso-3/datos.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RepoCertificacion\Certificacion.PostulacionWs\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vjose1903/git/personal/novac-server/dgii_signature_microservice/src/utils/paso-3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{762E0E45-7A45-4FC0-BB1E-78F104FDCDA3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2446A713-B6C6-CD4F-94EA-E235393DDB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{9C637CB2-FEC7-4A03-A305-FA9575F69409}"/>
+    <workbookView xWindow="43640" yWindow="2380" windowWidth="24240" windowHeight="13140" xr2:uid="{9C637CB2-FEC7-4A03-A305-FA9575F69409}"/>
   </bookViews>
   <sheets>
     <sheet name="ACEECF_Generadas" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="25">
   <si>
     <t>Version</t>
   </si>
@@ -75,7 +75,7 @@
     <t>131996035</t>
   </si>
   <si>
-    <t>08-01-2025 08:07:14</t>
+    <t>28-01-2025 08:01:01</t>
   </si>
   <si>
     <t>E310000000002</t>
@@ -112,8 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,9 +171,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -193,9 +192,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -233,7 +232,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -339,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -481,7 +480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -490,19 +489,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6EC857-6D12-4474-ADD1-3C3A796A1B2E}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="13.7109375" customWidth="1" style="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1" style="1"/>
-    <col min="4" max="4" width="17.28515625" customWidth="1" style="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1" style="1"/>
-    <col min="6" max="6" bestFit="1" width="14.7109375" customWidth="1" style="1"/>
-    <col min="7" max="7" width="8.28515625" customWidth="1" style="1"/>
-    <col min="8" max="8" bestFit="1" width="21.42578125" customWidth="1" style="1"/>
-    <col min="9" max="9" bestFit="1" width="30" customWidth="1" style="1"/>
+    <col min="1" max="2" width="13.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,7 +530,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -557,7 +556,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -571,7 +570,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="1">
-        <v>4674.35</v>
+        <v>4674.3500000000004</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -583,7 +582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -609,7 +608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -635,7 +634,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -661,7 +660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
@@ -687,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -713,7 +712,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -739,7 +738,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -768,6 +767,5 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>